--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/WASHINGTON_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/WASHINGTON_2013.xlsx
@@ -3804,7 +3804,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C192">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C570">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C656">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C657">
@@ -17574,7 +17574,7 @@
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C957">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1055">
